--- a/data/trans_orig/IP1015-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149858</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288653</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202937</t>
+          <t>202911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412128</t>
+          <t>412255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717150</t>
+          <t>716925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722027</t>
+          <t>722026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397488</t>
+          <t>1398189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403049</t>
+          <t>1403721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285691</t>
+          <t>285442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202984</t>
+          <t>202982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>424781</t>
+          <t>425062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162638</t>
+          <t>162911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317767</t>
+          <t>317781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203339</t>
+          <t>203293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413655</t>
+          <t>413642</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>704759</t>
+          <t>704531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742441</t>
+          <t>742599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747536</t>
+          <t>747538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448903</t>
+          <t>1448811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454385</t>
+          <t>1454383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200366</t>
+          <t>201033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408333</t>
+          <t>408468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740621</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1444446</t>
+          <t>1445035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1015-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148808</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149677</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>288098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,84 +1751,84 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1401</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4913</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206423</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202930</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206423</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>202911</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412255</t>
+          <t>412240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,92 +2094,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5775</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720626</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>717166</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722028</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720626</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>716925</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722026</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1398189</t>
+          <t>1398161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403721</t>
+          <t>1403049</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3855</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4047</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152411</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148997</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285442</t>
+          <t>285634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2416</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2615</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2417</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2314</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204918</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>202982</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>202783</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>637</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>425062</t>
+          <t>424959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3074</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3229</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3043</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165378</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>163519</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165378</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162911</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317781</t>
+          <t>317595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3789</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4416</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3740</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206335</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>203631</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206335</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203293</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413642</t>
+          <t>412966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2397</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5543</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746101</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>742708</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747535</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>706448</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>704531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>704509</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746101</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>742599</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747538</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1448811</t>
+          <t>1448660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454383</t>
+          <t>1454387</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1364</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4703</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5235</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4688</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204372</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>200862</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204372</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201033</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>408468</t>
+          <t>407921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,107 +5988,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1364</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>743480</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>740008</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>743480</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>740067</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1445035</t>
+          <t>1444289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
